--- a/data/b2_primavera/B2 Primavera 04-2026.xlsx
+++ b/data/b2_primavera/B2 Primavera 04-2026.xlsx
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>57741.01</v>
+        <v>57445.57</v>
       </c>
     </row>
     <row r="3">
@@ -4797,25 +4797,25 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>2699.61</v>
+        <v>2991.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46122</v>
+        <v>46121</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>14000</v>
+        <v>932.33</v>
       </c>
     </row>
     <row r="5">
@@ -4824,34 +4824,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>3600</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46124</v>
+        <v>46122</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4195.45</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="7">
@@ -4860,52 +4860,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1330.97</v>
+        <v>4209.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46126</v>
+        <v>46124</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>3656.79</v>
+        <v>1303.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46127</v>
+        <v>46125</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>9487.18</v>
+        <v>3212.85</v>
       </c>
     </row>
     <row r="10">
@@ -4914,93 +4914,93 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1402.17</v>
+        <v>7844.14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46130</v>
+        <v>46127</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>4133.54</v>
+        <v>1761.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46131</v>
+        <v>46128</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>4038.82</v>
+        <v>3252.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46132</v>
+        <v>46131</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>20324.7</v>
+        <v>3697.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46134</v>
+        <v>46132</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1059.03</v>
+        <v>20373.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46136</v>
+        <v>46132</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -5009,16 +5009,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1128.62</v>
+        <v>1484.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
@@ -5027,11 +5027,11 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1372.36</v>
+        <v>1116.84</v>
       </c>
     </row>
     <row r="17">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>4138.56</v>
+        <v>4159.03</v>
       </c>
     </row>
     <row r="18">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2024.68</v>
+        <v>2039.17</v>
       </c>
     </row>
   </sheetData>
